--- a/datos/2022-04-29 03 Estándar técnico - Queso vaca.xlsx
+++ b/datos/2022-04-29 03 Estándar técnico - Queso vaca.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{58FA9201-9A4B-4116-88FF-C37DC395546E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C009634-86AA-4AEA-ABCC-EE5AE4CEA075}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="8_{58FA9201-9A4B-4116-88FF-C37DC395546E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3CD420D-3ECF-48A9-8475-0A0384CF0B7D}"/>
   <bookViews>
-    <workbookView xWindow="10965" yWindow="255" windowWidth="15390" windowHeight="14250" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="10965" yWindow="255" windowWidth="15390" windowHeight="14250" tabRatio="675" activeTab="1" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Std con datos de csv fab_queso" sheetId="16" r:id="rId1"/>
+    <sheet name="Std con datos de csv fab_qu (2)" sheetId="17" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
@@ -24,6 +24,7 @@
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="__123Graph_AGRAFIND" hidden="1">#REF!</definedName>
@@ -504,7 +505,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="88">
   <si>
     <t>ESM</t>
   </si>
@@ -765,6 +766,9 @@
   </si>
   <si>
     <t>MG Pérdidas suero neta (%)</t>
+  </si>
+  <si>
+    <t>Ejemplo</t>
   </si>
 </sst>
 </file>
@@ -5552,4 +5556,873 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820F61A9-8AE9-42B4-98AA-B9B33D0F6B55}">
+  <dimension ref="A1:B109"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="26">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="45"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="47">
+        <v>0.49399999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="47">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="49">
+        <f>SUM(B6:B7)</f>
+        <v>0.51500000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="92">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="93">
+        <f>1-B10</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="50">
+        <f t="shared" ref="B12:B13" si="0">B38*B19/1000</f>
+        <v>0.25750000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="51">
+        <f t="shared" si="0"/>
+        <v>0.25750000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="95">
+        <v>3.3399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="95">
+        <v>3.1099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="101">
+        <f>B16/B17</f>
+        <v>1.0739549839228295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="43">
+        <f>B16*B25</f>
+        <v>34.543584867459195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="43">
+        <f>B17*B25</f>
+        <v>32.164835011316796</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="34">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="43">
+        <f>B25-SUM(B19:B22)</f>
+        <v>910.53064800922391</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="44">
+        <f>-0.2307*10^(-2)*B24^2-0.2655*B24+1040.51-B16*(-0.478*10^(-4)*B24^2+0.969*10^(-2)*B24+0.967)</f>
+        <v>1034.2390678879999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="44"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="102">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="102">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="102"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="103">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="1"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="97">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="43">
+        <f>B34*B48*1000</f>
+        <v>423.62953279999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="27">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="35">
+        <f>B8/B19*B10*1000</f>
+        <v>7.4543508147172819</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="36">
+        <f>B8/B20*B11*1000</f>
+        <v>8.0056372093748287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="1"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="96">
+        <f>1-B42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="96"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="38">
+        <v>0.94650000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="46">
+        <f>(-0.2307*10^(-2)*B24^2-0.2655*B24+1040.51-B34*100*(-0.478*10^(-4)*B24^2+0.969*10^(-2)*B24+0.967))/1000</f>
+        <v>0.98518496</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A50" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="52"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="98">
+        <f>'Std con datos de csv fab_qu (2)'!B3</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" s="98">
+        <f>'Std con datos de csv fab_qu (2)'!B4</f>
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="12">
+        <f>B53/B52</f>
+        <v>0.50909090909090915</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" s="12">
+        <f>(1-B52)/(1-B52*B54)</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="19">
+        <f>B52-B53</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="55"/>
+      <c r="B57" s="14"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="10">
+        <f>B96</f>
+        <v>32.164835011316796</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="71">
+        <v>0.96779999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="41">
+        <f>B63/B66</f>
+        <v>0.93453120425815051</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" s="11">
+        <f>B59*B58</f>
+        <v>31.129127323952396</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="13">
+        <f>B56*1000/B61</f>
+        <v>8.6735486411226095</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="11">
+        <f>B53*1000/B62</f>
+        <v>32.282057965580265</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" s="20">
+        <f>B66-B63</f>
+        <v>2.2615269018789306</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65" s="12">
+        <f>B64/B66</f>
+        <v>6.5468795741849536E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="11">
+        <f>B93</f>
+        <v>34.543584867459195</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="23">
+        <f>B66*B62</f>
+        <v>299.61546358665424</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B68" s="24">
+        <f>B58*B62</f>
+        <v>278.98326100433974</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B69" s="9">
+        <f>+B102/B62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="104">
+        <f>B64-B69</f>
+        <v>2.2615269018789306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="15">
+        <f>+B70/B66</f>
+        <v>6.5468795741849536E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="B72" s="16">
+        <f>+B66-B69</f>
+        <v>34.543584867459195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="21">
+        <f>B$72*B$62</f>
+        <v>299.61546358665424</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="22">
+        <f>B$58*B$62</f>
+        <v>278.98326100433974</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="74"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B76" s="75">
+        <f>'Std con datos de csv fab_qu (2)'!B42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77" s="75">
+        <f>'Std con datos de csv fab_qu (2)'!B43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="73"/>
+      <c r="B78" s="76">
+        <f>SUM(B76:B77)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="8"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="77">
+        <f>'Std con datos de csv fab_qu (2)'!B19</f>
+        <v>34.543584867459195</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="77">
+        <f>'Std con datos de csv fab_qu (2)'!B35</f>
+        <v>423.62953279999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="72"/>
+      <c r="B82" s="77"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" s="77">
+        <f>'Std con datos de csv fab_qu (2)'!B20</f>
+        <v>32.164835011316796</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="77">
+        <f>'Std con datos de csv fab_qu (2)'!B36</f>
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="83"/>
+      <c r="B85" s="77"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="88">
+        <f>+B93/B96</f>
+        <v>1.0739549839228295</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="87"/>
+      <c r="B87" s="88"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="85">
+        <f>'Std con datos de csv fab_qu (2)'!B25/1000</f>
+        <v>1.034239067888</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="86">
+        <f>'Std con datos de csv fab_qu (2)'!B48</f>
+        <v>0.98518496</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" s="84"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="18">
+        <f t="shared" ref="B91:B92" si="1">(B80*B76)</f>
+        <v>34.543584867459195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="63"/>
+      <c r="B93" s="18">
+        <f>SUM(B91:B92)</f>
+        <v>34.543584867459195</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B94" s="18">
+        <f t="shared" ref="B94:B95" si="2">B83*B76</f>
+        <v>32.164835011316796</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="82"/>
+      <c r="B96" s="18">
+        <f>SUM(B94:B95)</f>
+        <v>32.164835011316796</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" s="78">
+        <f>SUMPRODUCT(B88:B89,B76:B77)</f>
+        <v>1.034239067888</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="80"/>
+      <c r="B98" s="81"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="8"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" s="16">
+        <f>+B67*(B91)/B93</f>
+        <v>299.61546358665424</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" s="16">
+        <f>+B68*(B94)/B96</f>
+        <v>278.98326100433974</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" s="16">
+        <f>+B$67*(B92)/B$93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" s="17">
+        <f>+B$68*(B95)/B$96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="74"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B105" s="89">
+        <f>'Std con datos de csv fab_qu (2)'!B38</f>
+        <v>7.4543508147172819</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" s="90">
+        <f>'Std con datos de csv fab_qu (2)'!B39</f>
+        <v>8.0056372093748287</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B107" s="7">
+        <f t="shared" ref="B107:B108" si="3">B100*B105/1000</f>
+        <v>2.2334387750890725</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B108" s="6">
+        <f t="shared" si="3"/>
+        <v>2.2334387750890721</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="5">
+        <f>SUM(B107:B108)</f>
+        <v>4.466877550178145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/datos/2022-04-29 03 Estándar técnico - Queso vaca.xlsx
+++ b/datos/2022-04-29 03 Estándar técnico - Queso vaca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="8_{58FA9201-9A4B-4116-88FF-C37DC395546E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3CD420D-3ECF-48A9-8475-0A0384CF0B7D}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="8_{58FA9201-9A4B-4116-88FF-C37DC395546E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF6BB56-6232-453D-BC94-378486833A73}"/>
   <bookViews>
-    <workbookView xWindow="10965" yWindow="255" windowWidth="15390" windowHeight="14250" tabRatio="675" activeTab="1" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="1" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Std con datos de csv fab_queso" sheetId="16" r:id="rId1"/>
@@ -6009,7 +6009,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="71">
-        <v>0.96779999999999999</v>
+        <v>0.94650000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="B60" s="41">
         <f>B63/B66</f>
-        <v>0.93453120425815051</v>
+        <v>0.91396340652029273</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="B61" s="11">
         <f>B59*B58</f>
-        <v>31.129127323952396</v>
+        <v>30.444016338211348</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B62" s="13">
         <f>B56*1000/B61</f>
-        <v>8.6735486411226095</v>
+        <v>8.8687378498451785</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="B63" s="11">
         <f>B53*1000/B62</f>
-        <v>32.282057965580265</v>
+        <v>31.571572498885843</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B64" s="20">
         <f>B66-B63</f>
-        <v>2.2615269018789306</v>
+        <v>2.9720123685733526</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B65" s="12">
         <f>B64/B66</f>
-        <v>6.5468795741849536E-2</v>
+        <v>8.6036593479707213E-2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="B67" s="23">
         <f>B66*B62</f>
-        <v>299.61546358665424</v>
+        <v>306.35799858337452</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="B68" s="24">
         <f>B58*B62</f>
-        <v>278.98326100433974</v>
+        <v>285.26148969889067</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B70" s="104">
         <f>B64-B69</f>
-        <v>2.2615269018789306</v>
+        <v>2.9720123685733526</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B71" s="15">
         <f>+B70/B66</f>
-        <v>6.5468795741849536E-2</v>
+        <v>8.6036593479707213E-2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="B73" s="21">
         <f>B$72*B$62</f>
-        <v>299.61546358665424</v>
+        <v>306.35799858337452</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B74" s="22">
         <f>B$58*B$62</f>
-        <v>278.98326100433974</v>
+        <v>285.26148969889067</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="B100" s="16">
         <f>+B67*(B91)/B93</f>
-        <v>299.61546358665424</v>
+        <v>306.35799858337452</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="B101" s="16">
         <f>+B68*(B94)/B96</f>
-        <v>278.98326100433974</v>
+        <v>285.26148969889067</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B107" s="7">
         <f t="shared" ref="B107:B108" si="3">B100*B105/1000</f>
-        <v>2.2334387750890725</v>
+        <v>2.2836999963351334</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="B108" s="6">
         <f t="shared" si="3"/>
-        <v>2.2334387750890721</v>
+        <v>2.2836999963351334</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B109" s="5">
         <f>SUM(B107:B108)</f>
-        <v>4.466877550178145</v>
+        <v>4.5673999926702669</v>
       </c>
     </row>
   </sheetData>
